--- a/data/exports/daily_groups.xlsx
+++ b/data/exports/daily_groups.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,29 +424,183 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>CAP</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>KOPA</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>MI</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>КУ</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Р</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2337 ₽</t>
-        </is>
-      </c>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>72 ₽</t>
+          <t>2634 ₽</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>109 ₽</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2373 ₽</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3472 ₽</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2530 ₽</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2910 ₽</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>329 ₽</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>40 ₽</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3137 ₽</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3125 ₽</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>336 ₽</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1876 ₽</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>42 ₽</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2062 ₽</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>19215 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>522 ₽</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5661 ₽</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5401 ₽</t>
         </is>
       </c>
     </row>
